--- a/artfynd/A 2992-2023 artfynd.xlsx
+++ b/artfynd/A 2992-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2992-2023 artfynd.xlsx
+++ b/artfynd/A 2992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106822275</v>
+        <v>56512323</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bornjöns Naturreservat, Srm</t>
+          <t>NO Smedstorp vid trafikplats Salem, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656743.1945593046</v>
+        <v>656766</v>
       </c>
       <c r="R2" t="n">
-        <v>6567634.826312946</v>
+        <v>6567528</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,38 +757,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asplåga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Bornsjön</t>
-        </is>
-      </c>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>106822213</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -816,12 +797,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656767.9689349793</v>
+        <v>656768</v>
       </c>
       <c r="R3" t="n">
-        <v>6567556.919741958</v>
+        <v>6567557</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -864,19 +845,9 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +871,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Bornsjön</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106822275</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bornjöns Naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>656743</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6567635</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Bornsjön</t>
         </is>

--- a/artfynd/A 2992-2023 artfynd.xlsx
+++ b/artfynd/A 2992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56512323</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Bornsjön</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822213</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
           <t>Bornsjön</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>